--- a/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/9. IC卡充退表.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/9. IC卡充退表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="217">
   <si>
     <t>业务属性</t>
   </si>
@@ -254,9 +254,6 @@
   </si>
   <si>
     <t>数值</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
   <si>
     <t>0</t>
@@ -2102,52 +2099,52 @@
       <c r="Q4" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="6">
+        <v>22</v>
+      </c>
+      <c r="S4" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="U4" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="V4" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="W4" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="X4" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="Y4" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AA4" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AB4" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="AB4" s="6" t="s">
+      <c r="AC4" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC4" s="6" t="s">
+      <c r="AD4" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="AD4" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="5" ht="72" spans="1:30">
       <c r="A5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>94</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>69</v>
@@ -2162,10 +2159,10 @@
         <v>72</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
@@ -2180,55 +2177,55 @@
         <v>77</v>
       </c>
       <c r="P5" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="S5" s="6"/>
       <c r="U5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V5" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V5" s="6" t="s">
+      <c r="W5" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="X5" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X5" s="6" t="s">
+      <c r="Y5" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Z5" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="Z5" s="6" t="s">
-        <v>87</v>
-      </c>
       <c r="AA5" s="22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AB5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC5" s="6" t="s">
+      <c r="AD5" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="AD5" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="6" ht="72" spans="1:30">
       <c r="A6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>69</v>
@@ -2243,14 +2240,14 @@
         <v>72</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>75</v>
@@ -2268,52 +2265,52 @@
       <c r="Q6" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R6" s="6" t="s">
+      <c r="R6" s="6">
+        <v>22</v>
+      </c>
+      <c r="S6" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="U6" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U6" s="6" t="s">
+      <c r="V6" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V6" s="6" t="s">
+      <c r="W6" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W6" s="6" t="s">
+      <c r="X6" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="Y6" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y6" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z6" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA6" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="AA6" s="6" t="s">
+      <c r="AB6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC6" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="AB6" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC6" s="6" t="s">
+      <c r="AD6" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD6" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="7" ht="72" spans="1:30">
       <c r="A7" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>69</v>
@@ -2328,10 +2325,10 @@
         <v>72</v>
       </c>
       <c r="H7" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
@@ -2351,55 +2348,55 @@
       <c r="Q7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R7" s="6" t="s">
-        <v>80</v>
+      <c r="R7" s="6">
+        <v>22</v>
       </c>
       <c r="S7" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="T7" t="s">
         <v>116</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="W7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="X7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z7" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="U7" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="V7" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="W7" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="X7" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y7" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z7" s="6" t="s">
+      <c r="AA7" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="AA7" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="AB7" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC7" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD7" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD7" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="8" ht="72" spans="1:30">
       <c r="A8" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>69</v>
@@ -2414,10 +2411,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
@@ -2437,55 +2434,55 @@
       <c r="Q8" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R8" s="6" t="s">
-        <v>80</v>
+      <c r="R8" s="6">
+        <v>22</v>
       </c>
       <c r="S8" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="T8" t="s">
+        <v>116</v>
+      </c>
+      <c r="U8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="W8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="X8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA8" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="T8" t="s">
-        <v>117</v>
-      </c>
-      <c r="U8" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="W8" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="X8" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y8" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA8" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="AB8" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC8" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD8" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD8" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="9" ht="72" spans="1:30">
       <c r="A9" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>69</v>
@@ -2500,10 +2497,10 @@
         <v>72</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -2523,55 +2520,55 @@
       <c r="Q9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R9" s="6" t="s">
-        <v>80</v>
+      <c r="R9" s="6">
+        <v>22</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T9" t="s">
+        <v>116</v>
+      </c>
+      <c r="U9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V9" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="W9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="X9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z9" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="U9" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="V9" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="W9" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="X9" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y9" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="AA9" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AB9" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD9" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD9" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="10" ht="72" spans="1:30">
       <c r="A10" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>69</v>
@@ -2586,10 +2583,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -2609,52 +2606,52 @@
       <c r="Q10" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R10" s="6" t="s">
-        <v>80</v>
+      <c r="R10" s="6">
+        <v>22</v>
       </c>
       <c r="S10" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="U10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V10" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="W10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="X10" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y10" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z10" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA10" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="U10" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="V10" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="W10" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="X10" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y10" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z10" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA10" s="22" t="s">
-        <v>139</v>
-      </c>
       <c r="AB10" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC10" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD10" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD10" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:30">
       <c r="A11" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>69</v>
@@ -2669,14 +2666,14 @@
         <v>72</v>
       </c>
       <c r="H11" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>75</v>
@@ -2694,52 +2691,52 @@
       <c r="Q11" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R11" s="6" t="s">
-        <v>80</v>
+      <c r="R11" s="6">
+        <v>22</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V11" s="6" t="s">
+      <c r="W11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W11" s="6" t="s">
+      <c r="X11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X11" s="6" t="s">
+      <c r="Y11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y11" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z11" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AA11" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AB11" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC11" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD11" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD11" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="12" ht="72" spans="1:30">
       <c r="A12" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="C12" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>69</v>
@@ -2754,10 +2751,10 @@
         <v>72</v>
       </c>
       <c r="H12" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
@@ -2778,54 +2775,54 @@
         <v>79</v>
       </c>
       <c r="R12" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="T12" t="s">
         <v>152</v>
       </c>
-      <c r="S12" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="T12" t="s">
+      <c r="U12" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="W12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="X12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA12" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="U12" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="V12" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="W12" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="X12" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="Y12" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z12" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA12" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="AB12" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC12" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD12" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD12" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="13" ht="72" spans="1:30">
       <c r="A13" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="6" t="s">
         <v>156</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>157</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>69</v>
@@ -2840,14 +2837,14 @@
         <v>72</v>
       </c>
       <c r="H13" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>75</v>
@@ -2865,52 +2862,52 @@
       <c r="Q13" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R13" s="6" t="s">
+      <c r="R13" s="6">
+        <v>22</v>
+      </c>
+      <c r="S13" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S13" s="6" t="s">
+      <c r="U13" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U13" s="6" t="s">
+      <c r="V13" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V13" s="6" t="s">
+      <c r="W13" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W13" s="6" t="s">
+      <c r="X13" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X13" s="6" t="s">
+      <c r="Y13" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y13" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z13" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AA13" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AB13" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC13" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD13" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD13" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="14" ht="72" spans="1:30">
       <c r="A14" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>69</v>
@@ -2925,10 +2922,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
@@ -2948,52 +2945,52 @@
       <c r="Q14" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R14" s="6" t="s">
+      <c r="R14" s="6">
+        <v>22</v>
+      </c>
+      <c r="S14" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S14" s="6" t="s">
+      <c r="U14" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U14" s="6" t="s">
+      <c r="V14" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V14" s="6" t="s">
+      <c r="W14" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W14" s="6" t="s">
+      <c r="X14" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X14" s="6" t="s">
+      <c r="Y14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y14" s="6" t="s">
+      <c r="Z14" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="Z14" s="6" t="s">
+      <c r="AA14" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="AA14" s="6" t="s">
+      <c r="AB14" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="AB14" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="AC14" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD14" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD14" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="15" ht="72" spans="1:30">
       <c r="A15" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>69</v>
@@ -3008,10 +3005,10 @@
         <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>171</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
@@ -3026,55 +3023,55 @@
         <v>77</v>
       </c>
       <c r="P15" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q15" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="Q15" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="R15" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S15" s="6"/>
       <c r="U15" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V15" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V15" s="6" t="s">
+      <c r="W15" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W15" s="6" t="s">
+      <c r="X15" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X15" s="6" t="s">
+      <c r="Y15" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y15" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z15" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AA15" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB15" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="AB15" s="6" t="s">
-        <v>174</v>
-      </c>
       <c r="AC15" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD15" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD15" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="16" ht="72" spans="1:30">
       <c r="A16" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>69</v>
@@ -3089,10 +3086,10 @@
         <v>72</v>
       </c>
       <c r="H16" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
@@ -3101,7 +3098,7 @@
       </c>
       <c r="M16" s="6"/>
       <c r="N16" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>77</v>
@@ -3112,52 +3109,52 @@
       <c r="Q16" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R16" s="6" t="s">
+      <c r="R16" s="6">
+        <v>22</v>
+      </c>
+      <c r="S16" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S16" s="6" t="s">
+      <c r="U16" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="U16" s="6" t="s">
+      <c r="V16" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V16" s="6" t="s">
+      <c r="W16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W16" s="6" t="s">
+      <c r="X16" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X16" s="6" t="s">
+      <c r="Y16" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y16" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z16" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AB16" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC16" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD16" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD16" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="17" ht="72" spans="1:30">
       <c r="A17" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>69</v>
@@ -3172,10 +3169,10 @@
         <v>72</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
@@ -3190,53 +3187,55 @@
         <v>77</v>
       </c>
       <c r="P17" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q17" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="Q17" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="R17" s="6"/>
+      <c r="R17" s="6">
+        <v>7</v>
+      </c>
       <c r="S17" s="6"/>
       <c r="U17" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V17" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V17" s="6" t="s">
+      <c r="W17" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W17" s="6" t="s">
+      <c r="X17" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X17" s="6" t="s">
+      <c r="Y17" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y17" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z17" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA17" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="AA17" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="AB17" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD17" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD17" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="18" ht="72" spans="1:30">
       <c r="A18" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>69</v>
@@ -3251,10 +3250,10 @@
         <v>72</v>
       </c>
       <c r="H18" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
@@ -3274,48 +3273,50 @@
       <c r="Q18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R18" s="6"/>
+      <c r="R18" s="6">
+        <v>22</v>
+      </c>
       <c r="S18" s="6"/>
       <c r="U18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V18" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V18" s="6" t="s">
+      <c r="W18" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W18" s="6" t="s">
+      <c r="X18" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X18" s="6" t="s">
+      <c r="Y18" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y18" s="6" t="s">
+      <c r="Z18" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="Z18" s="6" t="s">
+      <c r="AA18" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="AA18" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="AB18" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AC18" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD18" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD18" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="19" ht="72" spans="1:30">
       <c r="A19" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>69</v>
@@ -3330,10 +3331,10 @@
         <v>72</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
@@ -3353,48 +3354,50 @@
       <c r="Q19" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R19" s="6"/>
+      <c r="R19" s="6">
+        <v>22</v>
+      </c>
       <c r="S19" s="6"/>
       <c r="U19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V19" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V19" s="6" t="s">
+      <c r="W19" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W19" s="6" t="s">
+      <c r="X19" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X19" s="6" t="s">
+      <c r="Y19" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y19" s="6" t="s">
+      <c r="Z19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="Z19" s="6" t="s">
+      <c r="AA19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="AA19" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="AB19" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AC19" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD19" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD19" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:30">
       <c r="A20" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>69</v>
@@ -3409,14 +3412,14 @@
         <v>72</v>
       </c>
       <c r="H20" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>75</v>
@@ -3434,48 +3437,50 @@
       <c r="Q20" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R20" s="6"/>
+      <c r="R20" s="6">
+        <v>22</v>
+      </c>
       <c r="S20" s="6"/>
       <c r="U20" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V20" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V20" s="6" t="s">
+      <c r="W20" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W20" s="6" t="s">
+      <c r="X20" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X20" s="6" t="s">
+      <c r="Y20" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y20" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z20" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB20" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC20" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD20" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD20" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="21" ht="72" spans="1:30">
       <c r="A21" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>207</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>69</v>
@@ -3490,14 +3495,14 @@
         <v>72</v>
       </c>
       <c r="H21" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>75</v>
@@ -3515,48 +3520,50 @@
       <c r="Q21" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R21" s="6"/>
+      <c r="R21" s="6">
+        <v>22</v>
+      </c>
       <c r="S21" s="6"/>
       <c r="U21" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V21" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V21" s="6" t="s">
+      <c r="W21" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W21" s="6" t="s">
+      <c r="X21" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X21" s="6" t="s">
+      <c r="Y21" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y21" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z21" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AA21" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB21" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC21" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD21" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD21" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="22" ht="72" spans="1:30">
       <c r="A22" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>69</v>
@@ -3571,14 +3578,14 @@
         <v>72</v>
       </c>
       <c r="H22" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>75</v>
@@ -3596,39 +3603,39 @@
       <c r="Q22" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R22" s="6" t="s">
-        <v>80</v>
+      <c r="R22" s="6">
+        <v>22</v>
       </c>
       <c r="S22" s="6"/>
       <c r="U22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="V22" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V22" s="6" t="s">
+      <c r="W22" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W22" s="6" t="s">
+      <c r="X22" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="X22" s="6" t="s">
+      <c r="Y22" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="Y22" s="6" t="s">
-        <v>86</v>
-      </c>
       <c r="Z22" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AB22" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AC22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD22" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="AD22" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
